--- a/resources/digital-products/files/dp-adv-return-on-time.xlsx
+++ b/resources/digital-products/files/dp-adv-return-on-time.xlsx
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="£#,##0.00"/>
+    <numFmt numFmtId="164" formatCode="$#,##0.00"/>
   </numFmts>
   <fonts count="10">
     <font>
@@ -505,7 +505,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:F22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
@@ -521,7 +521,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Catalogue return-on-time</t>
+          <t>Catalog return-on-time</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -544,7 +544,7 @@
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>Your owner-hour rate (£)</t>
+          <t>Your owner-hour rate ($)</t>
         </is>
       </c>
       <c r="B5" s="6" t="n">
@@ -564,7 +564,7 @@
       </c>
       <c r="B7" s="7" t="inlineStr">
         <is>
-          <t>Contribution (£)</t>
+          <t>Contribution ($)</t>
         </is>
       </c>
       <c r="C7" s="7" t="inlineStr">
@@ -579,7 +579,7 @@
       </c>
       <c r="E7" s="7" t="inlineStr">
         <is>
-          <t>Return/hour (£)</t>
+          <t>Return/hour ($)</t>
         </is>
       </c>
       <c r="F7" s="7" t="inlineStr">
@@ -591,7 +591,7 @@
     <row r="8">
       <c r="A8" s="8" t="inlineStr">
         <is>
-          <t>£15 printable</t>
+          <t>$15 printable</t>
         </is>
       </c>
       <c r="B8" s="8" t="n">
@@ -743,5 +743,6 @@
     <mergeCell ref="A20:C20"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
 </file>
--- a/resources/digital-products/files/dp-adv-return-on-time.xlsx
+++ b/resources/digital-products/files/dp-adv-return-on-time.xlsx
@@ -507,7 +507,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:F22"/>
+  <dimension ref="A1:F24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -541,6 +541,7 @@
         </is>
       </c>
     </row>
+    <row r="4"/>
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
@@ -556,6 +557,7 @@
         </is>
       </c>
     </row>
+    <row r="6"/>
     <row r="7">
       <c r="A7" s="7" t="inlineStr">
         <is>
@@ -712,6 +714,7 @@
         <v/>
       </c>
     </row>
+    <row r="16"/>
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
@@ -719,6 +722,7 @@
         </is>
       </c>
     </row>
+    <row r="18"/>
     <row r="19">
       <c r="A19" s="11" t="n"/>
       <c r="B19" s="11" t="n"/>
@@ -731,12 +735,17 @@
         </is>
       </c>
     </row>
+    <row r="21"/>
     <row r="22">
       <c r="A22" s="13" t="inlineStr">
         <is>
-          <t>ePORTS — your ecom source. eports.global.</t>
-        </is>
-      </c>
+          <t>ePORTS — your ecom source (eports.global)</t>
+        </is>
+      </c>
+    </row>
+    <row r="23"/>
+    <row r="24">
+      <c r="A24" s="13" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="1">
